--- a/tools/_out/orfs_gen_20261020/out/DesignTable_FS6565C_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/DesignTable_FS6565C_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BS2"/>
+  <dimension ref="A1:BQ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,290 +479,280 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>FSWA_CSANG@DRIVE</t>
+          <t>FSWA_MINR@DRIVE</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>FSWA_MINR@DRIVE</t>
+          <t>FSWA_THDL@DRIVE</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>FSWA_THDL@DRIVE</t>
+          <t>FSWA_RELANG@DRIVE</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>FSWA_RELANG@DRIVE</t>
+          <t>FSWA_RELR@DRIVE</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>FSWA_RELR@DRIVE</t>
+          <t>FSWA_STEMR@DRIVE</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>FSWA_STEMR@DRIVE</t>
+          <t>FSWA_HEADL@DRIVE</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>FSWA_HEADL@DRIVE</t>
+          <t>HELIXDIA@HELIXSK_A</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>HELIXDIA@HELIXSK_A</t>
+          <t>HEIGHT@HELIX_A</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>HEIGHT@HELIX_A</t>
+          <t>PITCH@HELIX_A</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>PITCH@HELIX_A</t>
+          <t>PROF_R@THDPROF_A</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>PROF_R@THDPROF_A</t>
+          <t>APEXR@THDPROF_A</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>APEXR@THDPROF_A</t>
+          <t>FSWA_CBR@DRIVE</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>FSWA_CBR@DRIVE</t>
+          <t>FSWA_CBD@DRIVE</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>FSWA_CBD@DRIVE</t>
+          <t>FSWB_BODYS@DRIVE</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>FSWB_BODYS@DRIVE</t>
+          <t>FSWB_NECKR@DRIVE</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>FSWB_NECKR@DRIVE</t>
+          <t>FSWB_NUTL@DRIVE</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>FSWB_NUTL@DRIVE</t>
+          <t>FSWB_SKIRTR@DRIVE</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>FSWB_SKIRTR@DRIVE</t>
+          <t>FSWB_SKIRTL@DRIVE</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>FSWB_SKIRTL@DRIVE</t>
+          <t>FSWB_SKIRTFR@DRIVE</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>FSWB_SKIRTFR@DRIVE</t>
+          <t>FSWB_NUTHEXL@DRIVE</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>FSWB_NUTHEXL@DRIVE</t>
+          <t>FSWB_NUTR@DRIVE</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>FSWB_NUTR@DRIVE</t>
+          <t>FSWB_SEAL@DRIVE</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>FSWB_SEAL@DRIVE</t>
+          <t>FSWB_MINR@DRIVE</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>FSWB_CSANG@DRIVE</t>
+          <t>FSWB_THDL@DRIVE</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>FSWB_MINR@DRIVE</t>
+          <t>FSWB_RELANG@DRIVE</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>FSWB_THDL@DRIVE</t>
+          <t>FSWB_RELR@DRIVE</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>FSWB_RELANG@DRIVE</t>
+          <t>FSWB_STEMR@DRIVE</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>FSWB_RELR@DRIVE</t>
+          <t>FSWB_HEADL@DRIVE</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>FSWB_STEMR@DRIVE</t>
+          <t>HELIXDIA@HELIXSK_B</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>FSWB_HEADL@DRIVE</t>
+          <t>HEIGHT@HELIX_B</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>HELIXDIA@HELIXSK_B</t>
+          <t>PITCH@HELIX_B</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>HEIGHT@HELIX_B</t>
+          <t>PROF_R@THDPROF_B</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>PITCH@HELIX_B</t>
+          <t>APEXR@THDPROF_B</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>PROF_R@THDPROF_B</t>
+          <t>FSWB_CBR@DRIVE</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>APEXR@THDPROF_B</t>
+          <t>FSWB_CBD@DRIVE</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>FSWB_CBR@DRIVE</t>
+          <t>PROF_AX@THDPROF_B</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>FSWB_CBD@DRIVE</t>
+          <t>DA@BORE_A</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>PROF_AX@THDPROF_B</t>
+          <t>DEPTH@BORECUT_A</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>DA@BORE_A</t>
+          <t>DB@BORE_B</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>DEPTH@BORECUT_A</t>
+          <t>DEPTH@BORECUT_B</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>DB@BORE_B</t>
+          <t>START@BORECUT_B</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>DEPTH@BORECUT_B</t>
+          <t>DEPTH@HEXCUT</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>START@BORECUT_B</t>
+          <t>START@HEXCUT</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>DEPTH@HEXCUT</t>
+          <t>NUTHEXA@NUTHEXA</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>START@HEXCUT</t>
+          <t>DEPTH@NUTCUTA</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>NUTHEXA@NUTHEXA</t>
+          <t>NUTHEX@NUTHEX</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>DEPTH@NUTCUTA</t>
+          <t>DEPTH@NUTCUT</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>NUTHEX@NUTHEX</t>
+          <t>$PRP@PartNo</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>DEPTH@NUTCUT</t>
+          <t>$PRP@Description</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>$PRP@PartNo</t>
+          <t>$PRP@GeometryRoot</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>$PRP@Description</t>
+          <t>$PRP@EndA_Thread</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
         <is>
-          <t>$PRP@GeometryRoot</t>
+          <t>$PRP@EndB_Thread</t>
         </is>
       </c>
       <c r="BN1" t="inlineStr">
         <is>
-          <t>$PRP@EndA_Thread</t>
+          <t>$PRP@DataStatus</t>
         </is>
       </c>
       <c r="BO1" t="inlineStr">
         <is>
-          <t>$PRP@EndB_Thread</t>
+          <t>$PRP@AxialSource</t>
         </is>
       </c>
       <c r="BP1" t="inlineStr">
         <is>
-          <t>$PRP@DataStatus</t>
+          <t>$COMMENT</t>
         </is>
       </c>
       <c r="BQ1" t="inlineStr">
-        <is>
-          <t>$PRP@AxialSource</t>
-        </is>
-      </c>
-      <c r="BR1" t="inlineStr">
-        <is>
-          <t>$COMMENT</t>
-        </is>
-      </c>
-      <c r="BS1" t="inlineStr">
         <is>
           <t>$PRP@OMiSKU</t>
         </is>
@@ -811,139 +801,139 @@
         <v>0.571</v>
       </c>
       <c r="N2" t="n">
-        <v>60</v>
+        <v>0.54864</v>
       </c>
       <c r="O2" t="n">
+        <v>0.45364</v>
+      </c>
+      <c r="P2" t="n">
+        <v>45</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.5485</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.09728</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.5356</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="W2" t="n">
         <v>0.54864</v>
       </c>
-      <c r="P2" t="n">
+      <c r="X2" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.691</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.024</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.79674</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.54864</v>
+      </c>
+      <c r="AK2" t="n">
         <v>0.45364</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="AL2" t="n">
         <v>45</v>
       </c>
-      <c r="R2" t="n">
+      <c r="AM2" t="n">
         <v>0.6</v>
       </c>
-      <c r="S2" t="n">
+      <c r="AN2" t="n">
         <v>0.5485</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AO2" t="n">
         <v>0.256</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AP2" t="n">
         <v>1.09728</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AQ2" t="n">
         <v>0.5356</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AR2" t="n">
         <v>0.08333</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AS2" t="n">
         <v>0.54864</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AT2" t="n">
         <v>0.59375</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AU2" t="n">
         <v>0.604</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AV2" t="n">
         <v>0.05</v>
       </c>
-      <c r="AB2" t="n">
-        <v>1.691</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.468</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.024</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0.608</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0.161</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0.599</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.79674</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.571</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0.54864</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0.45364</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>45</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0.5485</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0.256</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.09728</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0.5356</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0.08333</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0.54864</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.59375</v>
-      </c>
       <c r="AW2" t="n">
-        <v>0.604</v>
+        <v>3.882</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.05</v>
+        <v>0.55</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.882</v>
+        <v>1.941</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.55</v>
       </c>
       <c r="BA2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BB2" t="n">
         <v>1.941</v>
       </c>
-      <c r="BB2" t="n">
-        <v>0.55</v>
-      </c>
       <c r="BC2" t="n">
-        <v>1.39</v>
+        <v>0.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.941</v>
+        <v>1.691</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.5</v>
+        <v>1.38</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.691</v>
+        <v>0.599</v>
       </c>
       <c r="BG2" t="n">
         <v>1.38</v>
@@ -951,53 +941,47 @@
       <c r="BH2" t="n">
         <v>0.599</v>
       </c>
-      <c r="BI2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.599</v>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>FS6565-12-12</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>ORFS Double Female Swivel Straight (female face-seal swivel x female face-seal swivel) - swivel nut mouth counterbored (-10 up), 1 3/16-12 UN (female O-ring face-seal swivel, SAE J1453) x 1 3/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
+        </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>FS6565-12-12</t>
+          <t>FS6565C</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>ORFS Double Female Swivel Straight (female face-seal swivel x female face-seal swivel) - swivel nut mouth counterbored (-10 up), 1 3/16-12 UN (female O-ring face-seal swivel, SAE J1453) x 1 3/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>1 3/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>FS6565C</t>
+          <t>1 3/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>1 3/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>1 3/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>Air-Way FF6565 (s523, double-pass 2026-10-15, parts.air-way.com/api/series/523, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p7 FS6565-12-12 (ORFS-p007-t01) | MODEL: L45 seal face -&gt; seal face, body hex S1, nuts S(1) / S(2), bores D19(1) / D19(2): review table (Air-Way, staged FS table; OMi website list decides the parts); the row length runs to the stem seal face (Brennan FS6565-08-08: Air-Way L45 2.12 = seal face to seal face); the model length (LNUT, nut face to nut face) = L45 + the measured seal -&gt; nut face distance SEAL of the swivel at both ends; body hex between the two measured body faces; bore step at the body-hex mid-plane (ASSUMPTION, as 6565); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan)</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>Air-Way FF6565 = Brennan p7 on overall length, nut hex, body hex (rounding-only differences count as equal) | Air-Way calls it "Male ORFS / Female Double Swivel Union" but prints two nut hexes S(1) / S(2) (= Brennan FFSS-FFSS) | OMi parts file row 5622 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are measured on Brennan STEPs only (Air-Way 3D models not yet measured)</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
-        <is>
-          <t>Air-Way FF6565 (s523, double-pass 2026-10-15, parts.air-way.com/api/series/523, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p7 FS6565-12-12 (ORFS-p007-t01) | MODEL: L45 seal face -&gt; seal face, body hex S1, nuts S(1) / S(2), bores D19(1) / D19(2): review table (Air-Way, staged FS table; OMi website list decides the parts); the row length runs to the stem seal face (Brennan FS6565-08-08: Air-Way L45 2.12 = seal face to seal face); the model length (LNUT, nut face to nut face) = L45 + the measured seal -&gt; nut face distance SEAL of the swivel at both ends; body hex between the two measured body faces; bore step at the body-hex mid-plane (ASSUMPTION, as 6565); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); female face-seal SWIVEL end (SAE J1453), measured per size on the swivel leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSSW_MEAS; the straight BRENNAN_FS6565-08-08 has the same swivel: hex face -&gt; seal face 0.855, nut rear 0.461 behind the hex face): the row length runs to the stem SEAL face (FS6565-08-08: Air-Way L45 = Brennan seal face to seal face), the nut face is SEAL further out; nut hex = the row column where it equals Air-Way FF318 S to the rounding, else FF318 S of the dash (Q-FS-NUT, user yes); hex length, rear skirt cone, skirt, nut rear face and neck measured, the body face (= the body hex end) measured unless the row prints the hex length; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink (-04 ... -08) or 0.05 counterbore + 60deg countersink (-10 up), 45deg relief, a cone to the stem head, the stem head to the seal face; NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan)</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>Air-Way FF6565 = Brennan p7 on overall length, nut hex, body hex (rounding-only differences count as equal) | Air-Way calls it "Male ORFS / Female Double Swivel Union" but prints two nut hexes S(1) / S(2) (= Brennan FFSS-FFSS) | OMi parts file row 5622 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are measured on Brennan STEPs only (Air-Way 3D models not yet measured)</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
         <is>
           <t>FS6565-12-12</t>
         </is>
